--- a/static/data/exports/Retro_MN_GE_2019.xlsx
+++ b/static/data/exports/Retro_MN_GE_2019.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20172,7 +20172,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20909,7 +20909,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21134,7 +21134,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21209,7 +21209,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21721,7 +21721,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24382,7 +24382,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24532,7 +24532,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24607,7 +24607,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24682,7 +24682,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -26019,7 +26019,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26381,7 +26381,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26606,7 +26606,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26818,7 +26818,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27118,7 +27118,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27268,7 +27268,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27343,7 +27343,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27555,7 +27555,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27705,7 +27705,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27855,7 +27855,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27930,7 +27930,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28155,7 +28155,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28380,7 +28380,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28742,7 +28742,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -28892,7 +28892,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P386" t="n">
@@ -29042,7 +29042,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29117,7 +29117,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29192,7 +29192,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29267,7 +29267,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29404,7 +29404,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29704,7 +29704,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -29929,7 +29929,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30141,7 +30141,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30441,7 +30441,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30653,7 +30653,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30728,7 +30728,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -30878,7 +30878,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -30953,7 +30953,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -31028,7 +31028,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31178,7 +31178,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -31765,7 +31765,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -31840,7 +31840,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -32000,20 +32000,20 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1711800</v>
+        <v>1711801</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Angam Karung Kom</t>
+          <t>Leikhan Kaipu</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>19783</v>
+        <v>19781</v>
       </c>
       <c r="E428" t="n">
         <v>72</v>
@@ -32037,12 +32037,12 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Angam Karung Kom</t>
+          <t>Leikhan Kaipu</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -32052,11 +32052,11 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P428" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="Q428" t="b">
         <v>0</v>
@@ -32075,20 +32075,20 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>1711801</v>
+        <v>1711800</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Leikhan Kaipu</t>
+          <t>Angam Karung Kom</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>19781</v>
+        <v>19783</v>
       </c>
       <c r="E429" t="n">
         <v>72</v>
@@ -32112,12 +32112,12 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Leikhan Kaipu</t>
+          <t>Angam Karung Kom</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -32127,11 +32127,11 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="Q429" t="b">
         <v>0</v>
@@ -32202,7 +32202,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32352,7 +32352,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32427,7 +32427,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32577,7 +32577,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32714,7 +32714,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -32789,7 +32789,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -33014,7 +33014,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P443" t="n">
@@ -33239,7 +33239,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33376,7 +33376,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33451,7 +33451,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -33751,7 +33751,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P451" t="n">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -33901,7 +33901,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34188,7 +34188,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34263,7 +34263,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34413,7 +34413,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -34488,7 +34488,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34563,7 +34563,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P465" t="n">
@@ -34925,7 +34925,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35437,7 +35437,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -35512,7 +35512,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -35587,7 +35587,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35662,7 +35662,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -35737,7 +35737,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -35812,7 +35812,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -35887,7 +35887,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -35962,7 +35962,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36174,7 +36174,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36249,7 +36249,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36324,7 +36324,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36399,7 +36399,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -36549,7 +36549,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -36624,7 +36624,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -36761,7 +36761,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -36836,7 +36836,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -36911,7 +36911,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37061,7 +37061,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37211,7 +37211,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -37423,7 +37423,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37648,7 +37648,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -37723,7 +37723,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -37798,7 +37798,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -37948,7 +37948,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38160,7 +38160,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38310,7 +38310,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38460,7 +38460,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -38897,7 +38897,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39047,7 +39047,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39122,7 +39122,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39259,7 +39259,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39334,7 +39334,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39409,7 +39409,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -39559,7 +39559,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39634,7 +39634,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -39709,7 +39709,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40071,7 +40071,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40221,7 +40221,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40371,7 +40371,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40446,7 +40446,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -40521,7 +40521,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40658,7 +40658,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -40883,7 +40883,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -40958,7 +40958,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41033,7 +41033,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41108,7 +41108,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41258,7 +41258,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41333,7 +41333,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41470,7 +41470,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -41620,7 +41620,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -41695,7 +41695,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -41770,7 +41770,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -41845,7 +41845,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -41920,7 +41920,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42132,7 +42132,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42207,7 +42207,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42282,7 +42282,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -42357,7 +42357,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42432,7 +42432,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P573" t="n">
@@ -42794,7 +42794,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -42869,7 +42869,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -43019,7 +43019,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43094,7 +43094,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P578" t="n">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -43381,7 +43381,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -43456,7 +43456,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P583" t="n">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P584" t="n">
@@ -43606,7 +43606,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -43681,7 +43681,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -43756,7 +43756,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P587" t="n">
@@ -43831,7 +43831,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -43906,7 +43906,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -43981,7 +43981,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -44056,7 +44056,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P591" t="n">
@@ -44193,7 +44193,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44268,7 +44268,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P594" t="n">
@@ -44343,7 +44343,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -44418,7 +44418,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P596" t="n">
@@ -44493,7 +44493,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P597" t="n">
@@ -44568,7 +44568,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P598" t="n">
@@ -44643,7 +44643,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -44780,7 +44780,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -44855,7 +44855,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -44930,7 +44930,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P603" t="n">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P604" t="n">
@@ -45080,7 +45080,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P605" t="n">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P607" t="n">
@@ -45305,7 +45305,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P608" t="n">
@@ -45442,7 +45442,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P610" t="n">
@@ -45517,7 +45517,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P611" t="n">
@@ -45592,7 +45592,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P612" t="n">
@@ -45667,7 +45667,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P613" t="n">
@@ -45742,7 +45742,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P614" t="n">
@@ -45817,7 +45817,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P615" t="n">
@@ -45892,7 +45892,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P616" t="n">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P618" t="n">
@@ -46104,7 +46104,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P619" t="n">
@@ -46179,7 +46179,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P620" t="n">
@@ -46254,7 +46254,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P621" t="n">
@@ -46329,7 +46329,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P622" t="n">
@@ -46404,7 +46404,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P623" t="n">
@@ -46479,7 +46479,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P624" t="n">
@@ -46554,7 +46554,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P625" t="n">
@@ -46629,7 +46629,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P626" t="n">
@@ -46766,7 +46766,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P628" t="n">
@@ -46841,7 +46841,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P629" t="n">
@@ -46916,7 +46916,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P630" t="n">
@@ -46991,7 +46991,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P631" t="n">
@@ -47066,7 +47066,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P632" t="n">
@@ -47141,7 +47141,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P633" t="n">
@@ -47216,7 +47216,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P634" t="n">
@@ -47353,7 +47353,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P636" t="n">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P637" t="n">
